--- a/datasets/example1/MatchupTable_updated.xlsx
+++ b/datasets/example1/MatchupTable_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RealTwin\RealTwin tool development\bearing_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/ets_ornl_gov/Documents/Desktop/GithubProjects/RT-GitRep/datasets/example1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A29C0BD-B3C8-44FD-BDF7-986247D5ECE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3A29C0BD-B3C8-44FD-BDF7-986247D5ECE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB91D8BE-B67D-5A8C-9818-B1C4D6821123}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -4044,6 +4044,54 @@
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="A3:A18"/>
+    <mergeCell ref="I40:I47"/>
+    <mergeCell ref="L35:L39"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="L19:L34"/>
+    <mergeCell ref="G64:G79"/>
+    <mergeCell ref="I64:I79"/>
+    <mergeCell ref="H87:H102"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="H3:H18"/>
+    <mergeCell ref="H80:H86"/>
+    <mergeCell ref="H103:H106"/>
+    <mergeCell ref="A56:A63"/>
+    <mergeCell ref="A64:A79"/>
+    <mergeCell ref="A87:A102"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="H48:H55"/>
+    <mergeCell ref="A48:A55"/>
+    <mergeCell ref="G56:G63"/>
+    <mergeCell ref="G40:G47"/>
+    <mergeCell ref="N19:N34"/>
+    <mergeCell ref="G80:G86"/>
+    <mergeCell ref="L103:L106"/>
+    <mergeCell ref="A80:A86"/>
+    <mergeCell ref="A19:A34"/>
+    <mergeCell ref="H19:H34"/>
+    <mergeCell ref="G103:G106"/>
+    <mergeCell ref="I19:I34"/>
+    <mergeCell ref="I103:I106"/>
+    <mergeCell ref="G35:G39"/>
+    <mergeCell ref="I35:I39"/>
+    <mergeCell ref="G48:G55"/>
+    <mergeCell ref="N87:N102"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="N56:N63"/>
+    <mergeCell ref="K3:K106"/>
+    <mergeCell ref="L80:L86"/>
+    <mergeCell ref="H40:H47"/>
+    <mergeCell ref="H56:H63"/>
+    <mergeCell ref="H35:H39"/>
+    <mergeCell ref="N35:N39"/>
+    <mergeCell ref="I56:I63"/>
+    <mergeCell ref="N48:N55"/>
+    <mergeCell ref="N80:N86"/>
+    <mergeCell ref="I80:I86"/>
+    <mergeCell ref="L48:L55"/>
+    <mergeCell ref="L56:L63"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="L87:L102"/>
     <mergeCell ref="G19:G34"/>
@@ -4060,55 +4108,13 @@
     <mergeCell ref="I87:I102"/>
     <mergeCell ref="N64:N79"/>
     <mergeCell ref="N40:N47"/>
-    <mergeCell ref="L80:L86"/>
-    <mergeCell ref="H40:H47"/>
-    <mergeCell ref="H56:H63"/>
-    <mergeCell ref="H35:H39"/>
-    <mergeCell ref="N35:N39"/>
-    <mergeCell ref="I56:I63"/>
-    <mergeCell ref="N48:N55"/>
-    <mergeCell ref="N80:N86"/>
-    <mergeCell ref="I80:I86"/>
-    <mergeCell ref="N19:N34"/>
-    <mergeCell ref="G80:G86"/>
-    <mergeCell ref="L103:L106"/>
-    <mergeCell ref="A80:A86"/>
-    <mergeCell ref="A19:A34"/>
-    <mergeCell ref="H19:H34"/>
-    <mergeCell ref="G103:G106"/>
-    <mergeCell ref="I19:I34"/>
-    <mergeCell ref="I103:I106"/>
-    <mergeCell ref="G35:G39"/>
-    <mergeCell ref="I35:I39"/>
-    <mergeCell ref="G48:G55"/>
-    <mergeCell ref="N87:N102"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="N56:N63"/>
-    <mergeCell ref="K3:K106"/>
-    <mergeCell ref="G64:G79"/>
-    <mergeCell ref="I64:I79"/>
-    <mergeCell ref="H87:H102"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="H3:H18"/>
-    <mergeCell ref="H80:H86"/>
-    <mergeCell ref="H103:H106"/>
-    <mergeCell ref="A56:A63"/>
-    <mergeCell ref="A64:A79"/>
-    <mergeCell ref="A87:A102"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="H48:H55"/>
-    <mergeCell ref="L48:L55"/>
-    <mergeCell ref="A48:A55"/>
-    <mergeCell ref="G56:G63"/>
-    <mergeCell ref="L56:L63"/>
-    <mergeCell ref="G40:G47"/>
-    <mergeCell ref="A3:A18"/>
-    <mergeCell ref="I40:I47"/>
-    <mergeCell ref="L35:L39"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="L19:L34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{db3dbd43-4c4b-4544-9f8a-0553f9f5f25e}" enabled="0" method="" siteId="{db3dbd43-4c4b-4544-9f8a-0553f9f5f25e}" removed="1"/>
+</clbl:labelList>
 </file>